--- a/out/MLP-mamba2_repeat_4_000006.xlsx
+++ b/out/MLP-mamba2_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.254026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003128222096160753</v>
+        <v>-0.0003187095611483092</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4026263409910837</v>
+        <v>0.4102038210157579</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.806015066578293</v>
+        <v>0.8211843668648274</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09298306858678258</v>
+        <v>-0.09473302018338621</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.254026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3090611464411744</v>
+        <v>0.3148094066781821</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8273593729251539</v>
+        <v>1.052801181987312</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.965427358179969</v>
+        <v>2.422508143875183</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.158305831513631</v>
+        <v>0.201441581477453</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.453472403560454</v>
+        <v>1.771053891920558</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2772878948554011</v>
+        <v>0.3528440342924853</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.849819837926228</v>
+        <v>2.275399435489058</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1518529418944903</v>
+        <v>0.1932304716451473</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.875998821448659</v>
+        <v>2.308711778800423</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06271747648045552</v>
+        <v>0.07980699886033336</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.849421643296335</v>
+        <v>2.274892739107805</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07814059364344086</v>
+        <v>0.09943267200476756</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.94299588095038</v>
+        <v>2.393964479504441</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04705014038626072</v>
+        <v>0.05987072190792552</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.958903724088574</v>
+        <v>2.41420695853782</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03577165311867397</v>
+        <v>0.04551874160966376</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.983375603149405</v>
+        <v>2.445346954667643</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01582110087575931</v>
+        <v>0.02013305787282807</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.979216191904165</v>
+        <v>2.440054182118801</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01255309261819042</v>
+        <v>0.0159757330334226</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.988497582471814</v>
+        <v>2.451865339479709</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006223685855629567</v>
+        <v>0.007919689474150388</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.988381415888184</v>
+        <v>2.451718903440779</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003616954928308779</v>
+        <v>0.004603173981077193</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.989388350043265</v>
+        <v>2.453001376293509</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001804522863781575</v>
+        <v>0.002299086990538597</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.989381097065147</v>
+        <v>2.452993507549667</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008890155785007095</v>
+        <v>0.001133360672303154</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.989353431364695</v>
+        <v>2.4529596910927</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000515673833352827</v>
+        <v>0.0006558552500247418</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.989492417003745</v>
+        <v>2.45313744209611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001690936688898088</v>
+        <v>0.0002159650412832189</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.989314504212841</v>
+        <v>2.452912975861501</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>0.0001050437662162811</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.989310473369611</v>
+        <v>2.452909207357645</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>5.615490325271265e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.989313240302476</v>
+        <v>2.452914162998576</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>2.344216536355913e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.989306688416747</v>
+        <v>2.452907224628689</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.989307066984992</v>
+        <v>2.452909218578483</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.989300400021122</v>
+        <v>2.452901884184339</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.989296537946026</v>
+        <v>2.452898398964031</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.989291990633841</v>
+        <v>2.452893851651846</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.989292080578491</v>
+        <v>2.452893941596496</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.989291222644906</v>
+        <v>2.452893083662911</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.989291450965941</v>
+        <v>2.452893311983946</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.989290655301729</v>
+        <v>2.452892516319734</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.989290717571102</v>
+        <v>2.452892578589107</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.989290745246379</v>
+        <v>2.452892606264384</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.989290897460402</v>
+        <v>2.452892758478407</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.98929055151944</v>
+        <v>2.452892412537445</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.989290627626452</v>
+        <v>2.452892488644457</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.989290793678113</v>
+        <v>2.452892654696119</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.989291153456713</v>
+        <v>2.452893014474718</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.989291174213171</v>
+        <v>2.452893035231176</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.989291277995459</v>
+        <v>2.452893139013465</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.989291506316494</v>
+        <v>2.4528933673345</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.989291381777748</v>
+        <v>2.452893242795753</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.989291409453025</v>
+        <v>2.45289327047103</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.989291464803579</v>
+        <v>2.452893325821584</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.989291727718709</v>
+        <v>2.452893588736715</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.989291644692879</v>
+        <v>2.452893505710884</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.989291437128302</v>
+        <v>2.452893298146307</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.989291450965941</v>
+        <v>2.452893311983946</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.989291589342325</v>
+        <v>2.45289345036033</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.989291305670736</v>
+        <v>2.452893166688741</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.989291132700256</v>
+        <v>2.452892993718261</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.989291028917967</v>
+        <v>2.452892889935973</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.989291174213171</v>
+        <v>2.452893035231176</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.989291416371844</v>
+        <v>2.45289327738985</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.989291243401363</v>
+        <v>2.452893104419369</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.989290945892137</v>
+        <v>2.452892806910142</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.989290932054498</v>
+        <v>2.452892793072503</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.989290565357078</v>
+        <v>2.452892426375084</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.989290565357078</v>
+        <v>2.452892426375084</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.989290503087705</v>
+        <v>2.452892364105711</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.989290399305417</v>
+        <v>2.452892260323422</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.989290226334936</v>
+        <v>2.452892087352941</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.989290274766671</v>
+        <v>2.452892135784676</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.989289914988071</v>
+        <v>2.452891776006076</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.989289873475155</v>
+        <v>2.452891734493161</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.989289928825709</v>
+        <v>2.452891789843714</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.989289984176263</v>
+        <v>2.452891845194269</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.989290025689179</v>
+        <v>2.452891886707184</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.989289755855228</v>
+        <v>2.452891616873234</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.989289811205782</v>
+        <v>2.452891672223787</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.989289956500986</v>
+        <v>2.452891817518991</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.98928992190689</v>
+        <v>2.452891782924895</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.989289908069252</v>
+        <v>2.452891769087257</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.989289998013902</v>
+        <v>2.452891859031907</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.854026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.989290316279586</v>
+        <v>2.452892177297591</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.989290136390286</v>
+        <v>2.452891997408291</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.989290177903202</v>
+        <v>2.452892038921207</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.254026995542006</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.989289991095082</v>
+        <v>2.452891852113088</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.989290060283274</v>
+        <v>2.45289192130128</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.989289859637517</v>
+        <v>2.452891720655523</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.989289901150432</v>
+        <v>2.452891762168438</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.254026995542006</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.989289928825709</v>
+        <v>2.452891789843714</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000006.xlsx
+++ b/out/MLP-mamba2_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.854026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003128222096160753</v>
+        <v>-0.0001668221380552277</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4026263409910837</v>
+        <v>0.2147130864962911</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.806015066578293</v>
+        <v>0.4298325134352252</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09298306858678258</v>
+        <v>-0.04958607707343127</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.1649601872848044</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3093304501946852</v>
+        <v>0.1649601872848044</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3090611464411744</v>
+        <v>0.1648061758761858</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8273593729251539</v>
+        <v>0.4731563552195135</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.965427358179969</v>
+        <v>1.112061051208309</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.158305831513631</v>
+        <v>0.09053307511258089</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.453472403560454</v>
+        <v>0.8192804914779398</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2772878948554011</v>
+        <v>0.1585772670435626</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.849819837926228</v>
+        <v>1.045946640416554</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1518529418944903</v>
+        <v>0.08684268215426617</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.875998821448659</v>
+        <v>1.060918095171762</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06271747648045552</v>
+        <v>0.03586729244464827</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.849421643296335</v>
+        <v>1.04571887667944</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07814059364344086</v>
+        <v>0.04468805888245835</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.94299588095038</v>
+        <v>1.09923332860754</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04705014038626072</v>
+        <v>0.02690739331707426</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.958903724088574</v>
+        <v>1.108330913230846</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03577165311867397</v>
+        <v>0.02045685238849709</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.983375603149405</v>
+        <v>1.122326342607348</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01582110087575931</v>
+        <v>0.009046018313376236</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.979216191904165</v>
+        <v>1.119945377452469</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01255309261819042</v>
+        <v>0.007178259244146682</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.988497582471814</v>
+        <v>1.125251680965031</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006223685855629567</v>
+        <v>0.003557107894946387</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.988381415888184</v>
+        <v>1.125183106179854</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003616954928308779</v>
+        <v>0.002066350930888233</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.989388350043265</v>
+        <v>1.125756818724769</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001804522863781575</v>
+        <v>0.001030675465444117</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.989381097065147</v>
+        <v>1.125750529238901</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008890155785007095</v>
+        <v>0.000506687372903943</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.989353431364695</v>
+        <v>1.125732576387031</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000515673833352827</v>
+        <v>0.0002920510972333436</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.989492417003745</v>
+        <v>1.12580972204008</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001690936688898088</v>
+        <v>9.320668501476395e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.989314504212841</v>
+        <v>1.125706074480287</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>4.440740523996295e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.989310473369611</v>
+        <v>1.125701635021744</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>2.190815743119357e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.989313240302476</v>
+        <v>1.125701216149512</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>9.221082681779568e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.989306688416747</v>
+        <v>1.125695285018074</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.989307066984992</v>
+        <v>1.125693512159021</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.989300400021122</v>
+        <v>1.125687512625424</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.989296537946026</v>
+        <v>1.12568327001527</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.989291990633841</v>
+        <v>1.125683498336305</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.989292080578491</v>
+        <v>1.125683588280955</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.989291222644906</v>
+        <v>1.12568273034737</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.989291450965941</v>
+        <v>1.125682958668405</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.989290655301729</v>
+        <v>1.125682163004194</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.989290717571102</v>
+        <v>1.125682225273566</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.989290745246379</v>
+        <v>1.125682252948843</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.989290897460402</v>
+        <v>1.125682405162866</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.98929055151944</v>
+        <v>1.125682059221905</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.989290627626452</v>
+        <v>1.125682135328916</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.989290793678113</v>
+        <v>1.125682301380578</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.989291153456713</v>
+        <v>1.125682661159178</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.989291174213171</v>
+        <v>1.125682681915636</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.989291277995459</v>
+        <v>1.125682785697924</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.989291506316494</v>
+        <v>1.125683014018959</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.989291381777748</v>
+        <v>1.125682889480213</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.989291409453025</v>
+        <v>1.12568291715549</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.989291464803579</v>
+        <v>1.125682972506044</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.989291727718709</v>
+        <v>1.125683235421174</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.989291644692879</v>
+        <v>1.125683152395343</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.989291437128302</v>
+        <v>1.125682944830766</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.989291450965941</v>
+        <v>1.125682958668405</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.989291589342325</v>
+        <v>1.12568309704479</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.989291305670736</v>
+        <v>1.125682813373201</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.989291132700256</v>
+        <v>1.12568264040272</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.989291028917967</v>
+        <v>1.125682536620432</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.989291174213171</v>
+        <v>1.125682681915636</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.989291416371844</v>
+        <v>1.125682924074309</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.989291243401363</v>
+        <v>1.125682751103828</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.989290945892137</v>
+        <v>1.125682453594601</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.989290932054498</v>
+        <v>1.125682439756962</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.989290565357078</v>
+        <v>1.125682073059543</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.989290565357078</v>
+        <v>1.125682073059543</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.989290503087705</v>
+        <v>1.12568201079017</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.989290399305417</v>
+        <v>1.125681907007881</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.989290226334936</v>
+        <v>1.125681734037401</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.989290274766671</v>
+        <v>1.125681782469135</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.989289914988071</v>
+        <v>1.125681422690535</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.989289873475155</v>
+        <v>1.12568138117762</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.989289928825709</v>
+        <v>1.125681436528174</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.989289984176263</v>
+        <v>1.125681491878728</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.989290025689179</v>
+        <v>1.125681533391643</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.989289755855228</v>
+        <v>1.125681263557693</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.989289811205782</v>
+        <v>1.125681318908247</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.989289956500986</v>
+        <v>1.125681464203451</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.98928992190689</v>
+        <v>1.125681429609355</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.989289908069252</v>
+        <v>1.125681415771716</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.989289998013902</v>
+        <v>1.125681505716366</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.989290316279586</v>
+        <v>1.125681823982051</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.989290136390286</v>
+        <v>1.125681644092751</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.989290177903202</v>
+        <v>1.125681685605666</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.989289991095082</v>
+        <v>1.125681498797547</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.989290060283274</v>
+        <v>1.125681567985739</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.989289859637517</v>
+        <v>1.125681367339982</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.989289901150432</v>
+        <v>1.125681408852897</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.254026995542006</v>
+        <v>0.06038435250706133</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.989289928825709</v>
+        <v>1.125681436528174</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000006.xlsx
+++ b/out/MLP-mamba2_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.5304235816001892</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.025618511228804</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.548204779624939</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.025618511228804</v>
+        <v>0.1199999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5990315079689026</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.7901557087898254</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.1877858340740204</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.7233967185020447</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.2926498651504517</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.5904588103294373</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.643790602684021</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.1961652785539627</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4733088612556458</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.336329847574234</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.7792312502861023</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2678697109222412</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2472430914640427</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2342865169048309</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5867523550987244</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.6475129723548889</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.225618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.7889562249183655</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4256726205348969</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.1988491266965866</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3387968838214874</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.307668924331665</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.8206425309181213</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.230862483382225</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.9701181650161743</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6618388295173645</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.225618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5442190170288086</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3245165050029755</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.7274180054664612</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3432791233062744</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2637887299060822</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5356505513191223</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.8429917097091675</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4729017913341522</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4442004263401031</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.8087652921676636</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3343236446380615</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5115118026733398</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5390142202377319</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9268225431442261</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.977568507194519</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9452605843544006</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001668221380552277</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2147130864962911</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.2482177466154099</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4298325134352252</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04958607707343127</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.01140115410089493</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1649601872848044</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.8738908171653748</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1649601872848044</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.9311092495918274</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1648061758761858</v>
+        <v>0.1487550174629798</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4731563552195135</v>
+        <v>0.2220724527183046</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.2343748509883881</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.112061051208309</v>
+        <v>0.5933421210574857</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09053307511258089</v>
+        <v>0.04249106159216588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.9629455804824829</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8192804914779398</v>
+        <v>0.4559277202391059</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1585772670435626</v>
+        <v>0.07442712414977931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.741911768913269</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.045946640416554</v>
+        <v>0.5623117357381268</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.08684268215426617</v>
+        <v>0.04075900163180279</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2950434684753418</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.060918095171762</v>
+        <v>0.5693384631679523</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03586729244464827</v>
+        <v>0.01683406125898829</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.9750028848648071</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.04571887667944</v>
+        <v>0.5622048559150095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04468805888245835</v>
+        <v>0.0209733053068108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.9692725539207458</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.225618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.09923332860754</v>
+        <v>0.5873212124477022</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02690739331707426</v>
+        <v>0.01262836336797664</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.9731934070587158</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.108330913230846</v>
+        <v>0.5915902860940718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02045685238849709</v>
+        <v>0.009599664042752726</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6114320755004883</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.122326342607348</v>
+        <v>0.5981569335121708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009046018313376236</v>
+        <v>0.00424317769124753</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.8828389048576355</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.119945377452469</v>
+        <v>0.5970368500988474</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007178259244146682</v>
+        <v>0.003364674982507011</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.8106392621994019</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.125251680965031</v>
+        <v>0.5995243225849434</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003557107894946387</v>
+        <v>0.001665988815887771</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9790767431259155</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.125183106179854</v>
+        <v>0.5994894788253274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002066350930888233</v>
+        <v>0.0009666730490402668</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7548089623451233</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.125756818724769</v>
+        <v>0.59975636174072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001030675465444117</v>
+        <v>0.0004808365245201334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.01531934551894665</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.125750529238901</v>
+        <v>0.5997507568414505</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000506687372903943</v>
+        <v>0.000236470445640063</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4430108964443207</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.125732576387031</v>
+        <v>0.5997396442596696</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002920510972333436</v>
+        <v>0.0001351814166719149</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.04952045530080795</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.12580972204008</v>
+        <v>0.5997734096240291</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>9.320668501476395e-05</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.07197890430688858</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.125706074480287</v>
+        <v>0.5997218561803243</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.440740523996295e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3234701454639435</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.125701635021744</v>
+        <v>0.5997171185196988</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.190815743119357e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.1196699663996696</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.125701216149512</v>
+        <v>0.5997143102936427</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.9603136777877808</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.125695285018074</v>
+        <v>0.5997088447279239</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2244972139596939</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.125693512159021</v>
+        <v>0.599705460109473</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.7887624502182007</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.125687512625424</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.8208763003349304</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.12568327001527</v>
+        <v>0.5997001732142569</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.04611320421099663</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.125683498336305</v>
+        <v>0.5997004015352917</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.01078267488628626</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7048498062146814</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.125683588280955</v>
+        <v>0.5997004914799416</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2405770421028137</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.12568273034737</v>
+        <v>0.5996996335463568</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.03545105457305908</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.125682958668405</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4982815682888031</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.125682163004194</v>
+        <v>0.5996990662031798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1130109801888466</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.125682225273566</v>
+        <v>0.5996991284725529</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4595131278038025</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.125682252948843</v>
+        <v>0.5996991561478298</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5782777667045593</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.125682405162866</v>
+        <v>0.599699308361853</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1330859512090683</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.125682059221905</v>
+        <v>0.5996989624208913</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.7088972330093384</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.06136036706685288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.125682135328916</v>
+        <v>0.599699038527903</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.180625393986702</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.125682301380578</v>
+        <v>0.5996992045795645</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.9625281691551208</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.125682661159178</v>
+        <v>0.5996995643581645</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7190000414848328</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.225618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.125682681915636</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.8845858573913574</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.125682785697924</v>
+        <v>0.5996996888969107</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1179063394665718</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.125683014018959</v>
+        <v>0.5996999172179455</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.128701239824295</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.125682889480213</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3417984545230865</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.12568291715549</v>
+        <v>0.5996998203544761</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9078119397163391</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.125682972506044</v>
+        <v>0.59969987570503</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.03689747676253319</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.125683235421174</v>
+        <v>0.5997001386201608</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2004687786102295</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.125683152395343</v>
+        <v>0.5997000555943299</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4038576781749725</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.125682944830766</v>
+        <v>0.5996998480297532</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4304121136665344</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.125682958668405</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1088922396302223</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.12568309704479</v>
+        <v>0.5997000002437762</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.05167698115110397</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.125682813373201</v>
+        <v>0.5996997165721876</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.1407175809144974</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.12568264040272</v>
+        <v>0.5996995436017069</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.841957688331604</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.125682536620432</v>
+        <v>0.5996994398194183</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.7033880352973938</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.125682681915636</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.2938473224639893</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.06136036706685294</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.125682924074309</v>
+        <v>0.5996998272732955</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.01783404871821404</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7048498062146814</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.125682751103828</v>
+        <v>0.5996996543028145</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3215417563915253</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.125682453594601</v>
+        <v>0.5996993567935875</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.02081744745373726</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.125682439756962</v>
+        <v>0.5996993429559491</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3578789830207825</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.125682073059543</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.8002915382385254</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.125682073059543</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.07482948899269104</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.06136036706685288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.12568201079017</v>
+        <v>0.5996989139891568</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1370593458414078</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.125681907007881</v>
+        <v>0.5996988102068682</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3091005682945251</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.125681734037401</v>
+        <v>0.5996986372363875</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.05565283447504044</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.125681782469135</v>
+        <v>0.599698685668122</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1181747317314148</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.125681422690535</v>
+        <v>0.599698325889522</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5982241630554199</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.12568138117762</v>
+        <v>0.5996982843766065</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.6256852149963379</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.125681436528174</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2857503294944763</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.125681491878728</v>
+        <v>0.5996983950777143</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1305684149265289</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7048498062146814</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.125681533391643</v>
+        <v>0.5996984365906296</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2509516775608063</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.125681263557693</v>
+        <v>0.5996981667566795</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7705670595169067</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.125681318908247</v>
+        <v>0.5996982221072334</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2602404654026031</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.125681464203451</v>
+        <v>0.5996983674024374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5637059211730957</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.06136036706685288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.125681429609355</v>
+        <v>0.5996983328083412</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2566166818141937</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.125681415771716</v>
+        <v>0.5996983189707026</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.9857220649719238</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.125681505716366</v>
+        <v>0.5996984089153528</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.9210857748985291</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.125681823982051</v>
+        <v>0.5996987271810374</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.03631120547652245</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.125681644092751</v>
+        <v>0.5996985472917373</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.1072110235691071</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.125681685605666</v>
+        <v>0.5996985888046527</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.5902929306030273</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.125681498797547</v>
+        <v>0.5996984019965333</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.07918118685483932</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.125681567985739</v>
+        <v>0.5996984711847259</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3788705170154572</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.125681367339982</v>
+        <v>0.5996982705389681</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4859309196472168</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.125681408852897</v>
+        <v>0.5996983120518834</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.7017409801483154</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.06038435250706133</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.125681436528174</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000006.xlsx
+++ b/out/MLP-mamba2_repeat_4_000006.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.548204779624939</v>
+        <v>0.5482047200202942</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1199999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.7901557087898254</v>
+        <v>0.7901557683944702</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.1877858340740204</v>
+        <v>0.1877858191728592</v>
       </c>
       <c r="JB6" t="n">
         <v>0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.7233967185020447</v>
+        <v>0.7233966588973999</v>
       </c>
       <c r="JB7" t="n">
         <v>0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.2926498651504517</v>
+        <v>0.2926498353481293</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.336329847574234</v>
+        <v>0.3363298773765564</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2472430914640427</v>
+        <v>0.2472430616617203</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.2342865169048309</v>
+        <v>0.2342865616083145</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.6475129723548889</v>
+        <v>0.6475130319595337</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.7889562249183655</v>
+        <v>0.788956344127655</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.4256726205348969</v>
+        <v>0.4256725907325745</v>
       </c>
       <c r="JB21" t="n">
         <v>0.02000000000000007</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3387968838214874</v>
+        <v>0.3387969434261322</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.307668924331665</v>
+        <v>0.3076688945293427</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.6618388295173645</v>
+        <v>0.6618387699127197</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5442190170288086</v>
+        <v>0.5442190766334534</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3245165050029755</v>
+        <v>0.3245165348052979</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3432791233062744</v>
+        <v>0.343279093503952</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2637887299060822</v>
+        <v>0.2637887597084045</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.5356505513191223</v>
+        <v>0.5356504917144775</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.8429917097091675</v>
+        <v>0.8429917693138123</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.3343236446380615</v>
+        <v>0.3343237042427063</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.5115118026733398</v>
+        <v>0.5115118622779846</v>
       </c>
       <c r="JB40" t="n">
         <v>0.5799999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.9452605843544006</v>
+        <v>0.9452604651451111</v>
       </c>
       <c r="JB44" t="n">
         <v>0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.741911768913269</v>
+        <v>0.7419117093086243</v>
       </c>
       <c r="JB51" t="n">
         <v>0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.7548089623451233</v>
+        <v>0.7548090219497681</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.04952045530080795</v>
+        <v>0.04952047765254974</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.07197890430688858</v>
+        <v>0.07197893410921097</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3234701454639435</v>
+        <v>0.3234698474407196</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1196699663996696</v>
+        <v>0.1196700185537338</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2244972139596939</v>
+        <v>0.2244972735643387</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.8208763003349304</v>
+        <v>0.8208762407302856</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1600000000000001</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.04611320421099663</v>
+        <v>0.04611319303512573</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2405770421028137</v>
+        <v>0.2405771017074585</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.03545105457305908</v>
+        <v>0.03545108065009117</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4982815682888031</v>
+        <v>0.4982816874980927</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1130109801888466</v>
+        <v>0.1130110025405884</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1330859512090683</v>
+        <v>0.1330859214067459</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.180625393986702</v>
+        <v>0.1806254088878632</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.9625281691551208</v>
+        <v>0.9625282883644104</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1179063394665718</v>
+        <v>0.1179063692688942</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.128701239824295</v>
+        <v>0.1287012845277786</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3417984545230865</v>
+        <v>0.3417985141277313</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.03689747676253319</v>
+        <v>0.0368974506855011</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2004687786102295</v>
+        <v>0.2004688531160355</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4038576781749725</v>
+        <v>0.4038577377796173</v>
       </c>
       <c r="JB91" t="n">
         <v>0.1600000000000001</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1088922396302223</v>
+        <v>0.1088922843337059</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.05167698115110397</v>
+        <v>0.05167700350284576</v>
       </c>
       <c r="JB94" t="n">
         <v>0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.1407175809144974</v>
+        <v>0.1407175958156586</v>
       </c>
       <c r="JB95" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.7033880352973938</v>
+        <v>0.703387975692749</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.01783404871821404</v>
+        <v>0.01783403940498829</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.02081744745373726</v>
+        <v>0.02081745676696301</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.5799999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3578789830207825</v>
+        <v>0.3578790128231049</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.8002915382385254</v>
+        <v>0.8002915978431702</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.07482948899269104</v>
+        <v>0.07482950389385223</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3091005682945251</v>
+        <v>0.3091005086898804</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.6256852149963379</v>
+        <v>0.6256850957870483</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1600000000000001</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1305684149265289</v>
+        <v>0.1305684447288513</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2509516775608063</v>
+        <v>0.2509516477584839</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2566166818141937</v>
+        <v>0.2566167116165161</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.9210857748985291</v>
+        <v>0.9210858345031738</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1600000000000001</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.07918118685483932</v>
+        <v>0.07918116450309753</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3788705170154572</v>
+        <v>0.3788705766201019</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
